--- a/business_surveys/028_document_management_survey--business_surveys.xlsx
+++ b/business_surveys/028_document_management_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,15 +520,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>intro</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Introduction</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please take a few minutes to complete this survey.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -548,13 +552,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What type of document do you mostly handle?</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What type of documents do you mostly handle?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>e.g. pdf, doc, xls</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -574,10 +582,14 @@
           <t>How often do you use documents in your work?</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>e.g. daily, weekly, monthly</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -604,7 +616,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -624,10 +636,14 @@
           <t>What is your biggest document management challenge?</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>e.g. finding a document, organizing documents, etc.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -647,7 +663,11 @@
           <t>How many documents do you typically handle per day?</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Enter number of documents</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -673,7 +693,7 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -765,7 +785,7 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -800,12 +820,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>question_12</t>
+          <t>question_11_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Do you have any other feedback or suggestions?</t>
+          <t>Any other feedback or suggestions?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -823,12 +843,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>question_13</t>
+          <t>question_12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Do you have any other feedback or suggestions?</t>
+          <t>How satisfied are you with the current document management system?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -841,17 +861,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>question_14</t>
+          <t>question_12_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Do you have any other feedback or suggestions?</t>
+          <t>Would you be willing to pay for the proposed document management system?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -869,7 +889,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>question_15</t>
+          <t>question_13</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -879,236 +899,6 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>question_16</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Do you have any other feedback or suggestions?</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>question_17</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Do you have any other feedback or suggestions?</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>question_18</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Do you have any other feedback or suggestions?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>question_19</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Do you have any other feedback or suggestions?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>question_20</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Do you have any other feedback or suggestions?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>question_21</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Do you have any other feedback or suggestions?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>question_22</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Do you have any other feedback or suggestions?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>question_23</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Do you have any other feedback or suggestions?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>field_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Field 25</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>question_24</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Do you have any other feedback or suggestions?</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1125,10 +915,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1204,17 +994,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1016,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>daily</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1033,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
     </row>
@@ -1260,29 +1050,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>monthly</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>file_cabinet</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>file cabinet</t>
+          <t>rarely</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1084,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>cloud_storage</t>
+          <t>file_cabinet</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cloud storage</t>
+          <t>file cabinet</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1101,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>cloud_storage</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>cloud storage</t>
         </is>
       </c>
     </row>
@@ -1328,29 +1118,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>network_drive</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>network drive</t>
+          <t>email</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>network_drive</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>network drive</t>
         </is>
       </c>
     </row>
@@ -1362,29 +1152,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>question_10_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>very_likely</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>very likely</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1186,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>likely</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>likely</t>
+          <t>very likely</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1203,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_very_likely</t>
+          <t>likely</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>not very likely</t>
+          <t>likely</t>
         </is>
       </c>
     </row>
@@ -1430,12 +1220,97 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>not_very_likely</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>not very likely</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>question_10_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>not_at_all</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>not at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>question_10_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>no_opinion</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>no opinion</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>question_12_2_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>question_12_2_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>question_12_2_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>no_opinion</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>no opinion</t>
         </is>
       </c>
     </row>
